--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R0c2a9a26a41c4bca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R01d94fc6c89b4748"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R81ba2fdca7814356"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R23e95ea58c774378"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rc3befe249fd14894"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R2f0d4ec847584c28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rba80ce58985f4438"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R0d13bf641a824614"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R6aa151346c0e4cbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Re305fb39da2e4430"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -359,10 +359,10 @@
     </x:row>
     <x:row r="4" ht="33" customHeight="1">
       <x:c r="A4" s="5" t="str">
-        <x:v>弃用窗口</x:v>
+        <x:v>弃用周期</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
-        <x:v>output/reports/deprecation_windows.csv</x:v>
+        <x:v>output/reports/deprecation_periods.csv</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
         <x:v>CSV</x:v>
@@ -500,7 +500,7 @@
     </x:row>
     <x:row r="6" ht="33" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>deprecation_windows.csv</x:v>
+        <x:v>deprecation_periods.csv</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
         <x:v>validateCoupon结论</x:v>
@@ -514,7 +514,7 @@
     </x:row>
     <x:row r="7" ht="33" customHeight="1">
       <x:c r="A7" s="5" t="str">
-        <x:v>deprecation_windows.csv</x:v>
+        <x:v>deprecation_periods.csv</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
         <x:v>removeCartItem结论</x:v>
